--- a/research/traditional_assets/database/data/iceland/iceland_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_drugs_biotechnology.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.4474505723204995</v>
+        <v>-2.092621664050236</v>
       </c>
       <c r="H2">
-        <v>-2.294484911550468</v>
+        <v>-5.237048665620095</v>
       </c>
       <c r="I2">
-        <v>-1.681581685744017</v>
+        <v>-7.098901098901099</v>
       </c>
       <c r="J2">
-        <v>-1.681581685744017</v>
+        <v>-7.098901098901099</v>
       </c>
       <c r="K2">
-        <v>60.7</v>
+        <v>-595.7</v>
       </c>
       <c r="L2">
-        <v>0.631633714880333</v>
+        <v>-9.351648351648352</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,64 +621,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>12.8</v>
+        <v>68.3</v>
       </c>
       <c r="V2">
-        <v>0.005147798109792882</v>
+        <v>0.02240593117475314</v>
+      </c>
+      <c r="W2">
+        <v>2.148989898989899</v>
       </c>
       <c r="X2">
-        <v>0.1502921991148987</v>
+        <v>0.123747197345395</v>
+      </c>
+      <c r="Y2">
+        <v>2.025242701644504</v>
+      </c>
+      <c r="Z2">
+        <v>0.1895269265099673</v>
+      </c>
+      <c r="AA2">
+        <v>-1.345432906872954</v>
       </c>
       <c r="AB2">
-        <v>0.1303094676437922</v>
+        <v>0.1048406087261275</v>
+      </c>
+      <c r="AC2">
+        <v>-1.450273515599082</v>
       </c>
       <c r="AD2">
-        <v>636.8</v>
+        <v>1015</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>636.8</v>
+        <v>1015</v>
       </c>
       <c r="AG2">
-        <v>624</v>
+        <v>946.7</v>
       </c>
       <c r="AH2">
-        <v>0.2038869144814779</v>
+        <v>0.2497969630595821</v>
       </c>
       <c r="AI2">
-        <v>1.770856507230256</v>
+        <v>2.866421914713358</v>
       </c>
       <c r="AJ2">
-        <v>0.2006108342710175</v>
+        <v>0.2369712140175219</v>
       </c>
       <c r="AK2">
-        <v>1.799307958477509</v>
+        <v>3.312456263121063</v>
       </c>
       <c r="AL2">
-        <v>84.5</v>
+        <v>166.1</v>
       </c>
       <c r="AM2">
-        <v>-12.8</v>
+        <v>166.1</v>
       </c>
       <c r="AN2">
-        <v>-4.2088565763384</v>
+        <v>-2.30839208551285</v>
       </c>
       <c r="AO2">
-        <v>-1.912426035502959</v>
+        <v>-2.722456351595425</v>
       </c>
       <c r="AP2">
-        <v>-4.124256444150694</v>
+        <v>-2.153058903798044</v>
       </c>
       <c r="AQ2">
-        <v>12.625</v>
+        <v>-2.722456351595425</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.4474505723204995</v>
+        <v>-2.092621664050236</v>
       </c>
       <c r="H3">
-        <v>-2.294484911550468</v>
+        <v>-5.237048665620095</v>
       </c>
       <c r="I3">
-        <v>-1.681581685744017</v>
+        <v>-7.098901098901099</v>
       </c>
       <c r="J3">
-        <v>-1.681581685744017</v>
+        <v>-7.098901098901099</v>
       </c>
       <c r="K3">
-        <v>60.7</v>
+        <v>-595.7</v>
       </c>
       <c r="L3">
-        <v>0.631633714880333</v>
+        <v>-9.351648351648352</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,7 +737,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -731,64 +746,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>12.8</v>
+        <v>68.3</v>
       </c>
       <c r="V3">
-        <v>0.005147798109792882</v>
+        <v>0.02240593117475314</v>
+      </c>
+      <c r="W3">
+        <v>2.148989898989899</v>
       </c>
       <c r="X3">
-        <v>0.1502921991148987</v>
+        <v>0.123747197345395</v>
+      </c>
+      <c r="Y3">
+        <v>2.025242701644504</v>
+      </c>
+      <c r="Z3">
+        <v>0.1895269265099673</v>
+      </c>
+      <c r="AA3">
+        <v>-1.345432906872954</v>
       </c>
       <c r="AB3">
-        <v>0.1303094676437922</v>
+        <v>0.1048406087261275</v>
+      </c>
+      <c r="AC3">
+        <v>-1.450273515599082</v>
       </c>
       <c r="AD3">
-        <v>636.8</v>
+        <v>1015</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>636.8</v>
+        <v>1015</v>
       </c>
       <c r="AG3">
-        <v>624</v>
+        <v>946.7</v>
       </c>
       <c r="AH3">
-        <v>0.2038869144814779</v>
+        <v>0.2497969630595821</v>
       </c>
       <c r="AI3">
-        <v>1.770856507230256</v>
+        <v>2.866421914713358</v>
       </c>
       <c r="AJ3">
-        <v>0.2006108342710175</v>
+        <v>0.2369712140175219</v>
       </c>
       <c r="AK3">
-        <v>1.799307958477509</v>
+        <v>3.312456263121063</v>
       </c>
       <c r="AL3">
-        <v>84.5</v>
+        <v>166.1</v>
       </c>
       <c r="AM3">
-        <v>-12.8</v>
+        <v>166.1</v>
       </c>
       <c r="AN3">
-        <v>-4.2088565763384</v>
+        <v>-2.30839208551285</v>
       </c>
       <c r="AO3">
-        <v>-1.912426035502959</v>
+        <v>-2.722456351595425</v>
       </c>
       <c r="AP3">
-        <v>-4.124256444150694</v>
+        <v>-2.153058903798044</v>
       </c>
       <c r="AQ3">
-        <v>12.625</v>
+        <v>-2.722456351595425</v>
       </c>
     </row>
   </sheetData>
